--- a/dados/dados_brutos_207.xlsx
+++ b/dados/dados_brutos_207.xlsx
@@ -94907,13 +94907,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7A498E7-E1C1-41B8-A45F-8500DE8D1632}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A6413C7-9B7F-4E6F-90BB-F497B2683DCF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{157B2749-1E80-4491-BD4D-3E8C5E8D74A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C52EDCDF-B11E-4B79-8190-083FB4B5989C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FF68CE6-6041-4B4A-AAF5-3831E5600303}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63B71EEE-8AF2-4119-993E-27546622748D}"/>
 </file>
--- a/dados/dados_brutos_207.xlsx
+++ b/dados/dados_brutos_207.xlsx
@@ -107645,13 +107645,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98B16943-7ABB-45B2-8803-C0737EBAAAC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0B5B23A-1DC4-41D1-A4C9-AD6AEBBC4503}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F9FC40B-1B28-49A5-BF8C-E7C466A71422}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C38FF356-DEFF-4963-BE67-0D379477C9C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{063102D5-C7FD-43E0-BE98-D44EFB9BE8B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEA0FA95-8DDC-498D-8D97-8C37868E0D64}"/>
 </file>